--- a/output/Pacdora_Leads_2026-03-11.xlsx
+++ b/output/Pacdora_Leads_2026-03-11.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,25 +439,30 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Niche</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Latest_Update</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Channel_URL</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>One_Click_Action</t>
         </is>
@@ -466,544 +471,137 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Paking Duck</t>
+          <t>Summer Day Studios</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2410</v>
+        <v>5160</v>
       </c>
       <c r="C2" t="n">
-        <v>3605</v>
+        <v>2386</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>5.25%</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Hobby, Lifestyle</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>2026-03-10</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UC9-mnjHABxSU9pdiTk-3-Xw</t>
-        </is>
-      </c>
-      <c r="I2">
-        <f>HYPERLINK("mailto:?subject=Collab%20Proposal%3A%20AI%203D%20Tools%20for%20your%20Audience&amp;body=Hi%20Paking%20Duck%2C%0A%0ALove%20your%20content%21%20I%27m%20Nemo%20from%20Pacdora...", "Click to Email")</f>
+          <t>info@summerdaydesignstudio.com</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCBr0OyoIEuZN84zpr4Fwg9A</t>
+        </is>
+      </c>
+      <c r="J2">
+        <f>HYPERLINK("mailto:?subject=Collab%20Proposal%3A%20AI%203D%20Tools%20for%20your%20Audience&amp;body=Hi%20Summer%20Day%20Studios%2C%0A%0ALove%20your%20content%21%20I%27m%20Nemo%20from%20Pacdora...", "Click to Email")</f>
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Imad's Studio</t>
+          <t>Gfx Adobe</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11700</v>
+        <v>13300</v>
       </c>
       <c r="C3" t="n">
-        <v>127909</v>
+        <v>29654</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.01%</t>
+          <t>0.72%</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>Lifestyle, Hobby</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>US</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UCksBQwoOhP1GpnAsNbkt_Jw</t>
-        </is>
-      </c>
-      <c r="I3">
-        <f>HYPERLINK("mailto:?subject=Collab%20Proposal%3A%20AI%203D%20Tools%20for%20your%20Audience&amp;body=Hi%20Imad%27s%20Studio%2C%0A%0ALove%20your%20content%21%20I%27m%20Nemo%20from%20Pacdora...", "Click to Email")</f>
+          <t>hafizabdullahparacha@gmail.com</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCpf0GPWEENPTlBk9flmS3ZQ</t>
+        </is>
+      </c>
+      <c r="J3">
+        <f>HYPERLINK("mailto:?subject=Collab%20Proposal%3A%20AI%203D%20Tools%20for%20your%20Audience&amp;body=Hi%20Gfx%20Adobe%2C%0A%0ALove%20your%20content%21%20I%27m%20Nemo%20from%20Pacdora...", "Click to Email")</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Shailevisuals</t>
+          <t>Plastoseal Packaging Solutions</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6330</v>
+        <v>95000</v>
       </c>
       <c r="C4" t="n">
-        <v>1024</v>
+        <v>1946</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.23%</t>
+          <t>0.79%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCEYKyMNPjGYDvcaN5Ug0cHw</t>
-        </is>
-      </c>
-      <c r="I4">
-        <f>HYPERLINK("mailto:?subject=Collab%20Proposal%3A%20AI%203D%20Tools%20for%20your%20Audience&amp;body=Hi%20Shailevisuals%2C%0A%0ALove%20your%20content%21%20I%27m%20Nemo%20from%20Pacdora...", "Click to Email")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Swiss Pac India</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>12100</v>
-      </c>
-      <c r="C5" t="n">
-        <v>233726</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0.01%</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>info@swisspack.co.in</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UC9XkYXVFbPU-NMfHntBbSGg</t>
-        </is>
-      </c>
-      <c r="I5">
-        <f>HYPERLINK("mailto:?subject=Collab%20Proposal%3A%20AI%203D%20Tools%20for%20your%20Audience&amp;body=Hi%20Swiss%20Pac%20India%2C%0A%0ALove%20your%20content%21%20I%27m%20Nemo%20from%20Pacdora...", "Click to Email")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Tesla Packaging</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>90800</v>
-      </c>
-      <c r="C6" t="n">
-        <v>2193</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>1.23%</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCcO_nxt076xaihsUU8baicA</t>
-        </is>
-      </c>
-      <c r="I6">
-        <f>HYPERLINK("mailto:?subject=Collab%20Proposal%3A%20AI%203D%20Tools%20for%20your%20Audience&amp;body=Hi%20Tesla%20Packaging%2C%0A%0ALove%20your%20content%21%20I%27m%20Nemo%20from%20Pacdora...", "Click to Email")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Allison Turquoise</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>63800</v>
-      </c>
-      <c r="C7" t="n">
-        <v>135437</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>7.69%</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCRUBJ68jA9uZC95xqYyOY6Q</t>
-        </is>
-      </c>
-      <c r="I7">
-        <f>HYPERLINK("mailto:?subject=Collab%20Proposal%3A%20AI%203D%20Tools%20for%20your%20Audience&amp;body=Hi%20Allison%20Turquoise%2C%0A%0ALove%20your%20content%21%20I%27m%20Nemo%20from%20Pacdora...", "Click to Email")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Manufacturing by Informa</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1250</v>
-      </c>
-      <c r="C8" t="n">
-        <v>13047</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>0.01%</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCabB8XrVorPYkAlfcCXx4Sg</t>
-        </is>
-      </c>
-      <c r="I8">
-        <f>HYPERLINK("mailto:?subject=Collab%20Proposal%3A%20AI%203D%20Tools%20for%20your%20Audience&amp;body=Hi%20Manufacturing%20by%20Informa%2C%0A%0ALove%20your%20content%21%20I%27m%20Nemo%20from%20Pacdora...", "Click to Email")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>DESIGN WITH TOSHI</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>39900</v>
-      </c>
-      <c r="C9" t="n">
-        <v>11284</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2.92%</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCV4-qvioAT4tJvjbcOX28HA</t>
-        </is>
-      </c>
-      <c r="I9">
-        <f>HYPERLINK("mailto:?subject=Collab%20Proposal%3A%20AI%203D%20Tools%20for%20your%20Audience&amp;body=Hi%20DESIGN%20WITH%20TOSHI%2C%0A%0ALove%20your%20content%21%20I%27m%20Nemo%20from%20Pacdora...", "Click to Email")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>FRD Tutorial</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>31800</v>
-      </c>
-      <c r="C10" t="n">
-        <v>5109</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>0.85%</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>2026-03-10</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>engage@frdstudio.com</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UC9fDmdRmgzu5jQjV8yEsDIQ</t>
-        </is>
-      </c>
-      <c r="I10">
-        <f>HYPERLINK("mailto:?subject=Collab%20Proposal%3A%20AI%203D%20Tools%20for%20your%20Audience&amp;body=Hi%20FRD%20Tutorial%2C%0A%0ALove%20your%20content%21%20I%27m%20Nemo%20from%20Pacdora...", "Click to Email")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>AdjoTech</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>24800</v>
-      </c>
-      <c r="C11" t="n">
-        <v>8340</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>3.32%</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>adjotech@gmail.com</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCiIXjm3Z6NM1lO2M0RfE_fg</t>
-        </is>
-      </c>
-      <c r="I11">
-        <f>HYPERLINK("mailto:?subject=Collab%20Proposal%3A%20AI%203D%20Tools%20for%20your%20Audience&amp;body=Hi%20AdjoTech%2C%0A%0ALove%20your%20content%21%20I%27m%20Nemo%20from%20Pacdora...", "Click to Email")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Maria Tokar</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>27700</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1876</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>5.16%</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCTwKoFLLMymqtLSWK0B4tRw</t>
-        </is>
-      </c>
-      <c r="I12">
-        <f>HYPERLINK("mailto:?subject=Collab%20Proposal%3A%20AI%203D%20Tools%20for%20your%20Audience&amp;body=Hi%20Maria%20Tokar%2C%0A%0ALove%20your%20content%21%20I%27m%20Nemo%20from%20Pacdora...", "Click to Email")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Yadox Studio</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>78600</v>
-      </c>
-      <c r="C13" t="n">
-        <v>69972</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>1.79%</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCdS0wF1r7bWbH2kw8JwDDDQ</t>
-        </is>
-      </c>
-      <c r="I13">
-        <f>HYPERLINK("mailto:?subject=Collab%20Proposal%3A%20AI%203D%20Tools%20for%20your%20Audience&amp;body=Hi%20Yadox%20Studio%2C%0A%0ALove%20your%20content%21%20I%27m%20Nemo%20from%20Pacdora...", "Click to Email")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Omi | Creative Powerhouse</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>2290</v>
-      </c>
-      <c r="C14" t="n">
-        <v>12527</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>0.33%</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCZ5LiWmOAHJkBl82VgiMLZQ</t>
-        </is>
-      </c>
-      <c r="I14">
-        <f>HYPERLINK("mailto:?subject=Collab%20Proposal%3A%20AI%203D%20Tools%20for%20your%20Audience&amp;body=Hi%20Omi%20%7C%20Creative%20Powerhouse%2C%0A%0ALove%20your%20content%21%20I%27m%20Nemo%20from%20Pacdora...", "Click to Email")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>jelly</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>16400</v>
-      </c>
-      <c r="C15" t="n">
-        <v>37511</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>9.90%</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCA41V9J0USwfXqqTdhV0orQ</t>
-        </is>
-      </c>
-      <c r="I15">
-        <f>HYPERLINK("mailto:?subject=Collab%20Proposal%3A%20AI%203D%20Tools%20for%20your%20Audience&amp;body=Hi%20jelly%2C%0A%0ALove%20your%20content%21%20I%27m%20Nemo%20from%20Pacdora...", "Click to Email")</f>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCy1AMCQhdIts2WPg2u0lWrA</t>
+        </is>
+      </c>
+      <c r="J4">
+        <f>HYPERLINK("mailto:?subject=Collab%20Proposal%3A%20AI%203D%20Tools%20for%20your%20Audience&amp;body=Hi%20Plastoseal%20Packaging%20Solutions%2C%0A%0ALove%20your%20content%21%20I%27m%20Nemo%20from%20Pacdora...", "Click to Email")</f>
         <v/>
       </c>
     </row>

--- a/output/Pacdora_Leads_2026-03-11.xlsx
+++ b/output/Pacdora_Leads_2026-03-11.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,18 +471,18 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Summer Day Studios</t>
+          <t>Photoshop ideas</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5160</v>
+        <v>4990</v>
       </c>
       <c r="C2" t="n">
-        <v>2386</v>
+        <v>3908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.25%</t>
+          <t>2.77%</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -492,116 +492,335 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>info@summerdaydesignstudio.com</t>
-        </is>
-      </c>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UCBr0OyoIEuZN84zpr4Fwg9A</t>
+          <t>https://youtube.com/channel/UCptFOK9XAHold-lkA1coZ0Q</t>
         </is>
       </c>
       <c r="J2">
-        <f>HYPERLINK("mailto:?subject=Collab%20Proposal%3A%20AI%203D%20Tools%20for%20your%20Audience&amp;body=Hi%20Summer%20Day%20Studios%2C%0A%0ALove%20your%20content%21%20I%27m%20Nemo%20from%20Pacdora...", "Click to Email")</f>
+        <f>HYPERLINK("mailto:?subject=Collab%20Proposal%3A%20AI%203D%20Tools%20for%20your%20Audience&amp;body=Hi%20Photoshop%20ideas%2C%0A%0ALove%20your%20content%21%20I%27m%20Nemo%20from%20Pacdora...", "Click to Email")</f>
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Gfx Adobe</t>
+          <t>Creative Design Ideas</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13300</v>
+        <v>9670</v>
       </c>
       <c r="C3" t="n">
-        <v>29654</v>
+        <v>22689</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.10%</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Lifestyle, Hobby</t>
+          <t>Hobby, Technology, Lifestyle</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>hafizabdullahparacha@gmail.com</t>
-        </is>
-      </c>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UCpf0GPWEENPTlBk9flmS3ZQ</t>
+          <t>https://youtube.com/channel/UCyRPB7R3FfLf5b9M4qaqKfw</t>
         </is>
       </c>
       <c r="J3">
-        <f>HYPERLINK("mailto:?subject=Collab%20Proposal%3A%20AI%203D%20Tools%20for%20your%20Audience&amp;body=Hi%20Gfx%20Adobe%2C%0A%0ALove%20your%20content%21%20I%27m%20Nemo%20from%20Pacdora...", "Click to Email")</f>
+        <f>HYPERLINK("mailto:?subject=Collab%20Proposal%3A%20AI%203D%20Tools%20for%20your%20Audience&amp;body=Hi%20Creative%20Design%20Ideas%2C%0A%0ALove%20your%20content%21%20I%27m%20Nemo%20from%20Pacdora...", "Click to Email")</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Plastoseal Packaging Solutions</t>
+          <t>Blender Artsy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>95000</v>
+        <v>11600</v>
       </c>
       <c r="C4" t="n">
-        <v>1946</v>
+        <v>5086</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>5.61%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lifestyle</t>
+          <t>Lifestyle, Film, Entertainment</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ahmadsyed6166@gmail.com</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCV9UtSxsnYHGRnKT0qWnOCQ</t>
+        </is>
+      </c>
+      <c r="J4">
+        <f>HYPERLINK("mailto:?subject=Collab%20Proposal%3A%20AI%203D%20Tools%20for%20your%20Audience&amp;body=Hi%20Blender%20Artsy%2C%0A%0ALove%20your%20content%21%20I%27m%20Nemo%20from%20Pacdora...", "Click to Email")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Digital Arnab</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3320</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4474</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1.02%</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Hobby, Lifestyle, Technology</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCMgcII9Gs_UabeBzdMZi2BQ</t>
+        </is>
+      </c>
+      <c r="J5">
+        <f>HYPERLINK("mailto:?subject=Collab%20Proposal%3A%20AI%203D%20Tools%20for%20your%20Audience&amp;body=Hi%20Digital%20Arnab%2C%0A%0ALove%20your%20content%21%20I%27m%20Nemo%20from%20Pacdora...", "Click to Email")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Dena Nguyen</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>95500</v>
+      </c>
+      <c r="C6" t="n">
+        <v>38831</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2.99%</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Hobby, Lifestyle</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>hi@denanguyen.com</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UC8ME0E1icwddCikdomxrIVw</t>
+        </is>
+      </c>
+      <c r="J6">
+        <f>HYPERLINK("mailto:?subject=Collab%20Proposal%3A%20AI%203D%20Tools%20for%20your%20Audience&amp;body=Hi%20Dena%20Nguyen%2C%0A%0ALove%20your%20content%21%20I%27m%20Nemo%20from%20Pacdora...", "Click to Email")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Let's Design</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>77100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>8384</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2.40%</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Hobby, Technology, Lifestyle</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCDFlV2_DJhWZbpN2IBiLgWQ</t>
+        </is>
+      </c>
+      <c r="J7">
+        <f>HYPERLINK("mailto:?subject=Collab%20Proposal%3A%20AI%203D%20Tools%20for%20your%20Audience&amp;body=Hi%20Let%27s%20Design%2C%0A%0ALove%20your%20content%21%20I%27m%20Nemo%20from%20Pacdora...", "Click to Email")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Creators Desk</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>25900</v>
+      </c>
+      <c r="C8" t="n">
+        <v>25215</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>8.43%</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Lifestyle, Technology</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCI4D8BuZQdhUKrAkII1CcyQ</t>
+        </is>
+      </c>
+      <c r="J8">
+        <f>HYPERLINK("mailto:?subject=Collab%20Proposal%3A%20AI%203D%20Tools%20for%20your%20Audience&amp;body=Hi%20Creators%20Desk%2C%0A%0ALove%20your%20content%21%20I%27m%20Nemo%20from%20Pacdora...", "Click to Email")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Tr Bahadurpur</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>58100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2655</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2.76%</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Lifestyle, Hobby</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>2026-03-10</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCy1AMCQhdIts2WPg2u0lWrA</t>
-        </is>
-      </c>
-      <c r="J4">
-        <f>HYPERLINK("mailto:?subject=Collab%20Proposal%3A%20AI%203D%20Tools%20for%20your%20Audience&amp;body=Hi%20Plastoseal%20Packaging%20Solutions%2C%0A%0ALove%20your%20content%21%20I%27m%20Nemo%20from%20Pacdora...", "Click to Email")</f>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>trbahadurpur2@gmail.com</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UC1BEAxi3POi5tuTmS2Q-hTw</t>
+        </is>
+      </c>
+      <c r="J9">
+        <f>HYPERLINK("mailto:?subject=Collab%20Proposal%3A%20AI%203D%20Tools%20for%20your%20Audience&amp;body=Hi%20Tr%20Bahadurpur%2C%0A%0ALove%20your%20content%21%20I%27m%20Nemo%20from%20Pacdora...", "Click to Email")</f>
         <v/>
       </c>
     </row>
